--- a/app/analytical-backend/data/07_model_output/ml.xlsx
+++ b/app/analytical-backend/data/07_model_output/ml.xlsx
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.0009867029955283868</v>
+        <v>0.0009867029955283994</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -578,7 +578,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>64.34236092160945</v>
+        <v>64.3423609216093</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>288</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -624,7 +624,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0001726251966894671</v>
+        <v>0.0001726251966894652</v>
       </c>
       <c r="D2">
         <v>142</v>
@@ -644,7 +644,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>-4.396177626687803E-05</v>
+        <v>-4.396177626689313E-05</v>
       </c>
       <c r="D3">
         <v>-237</v>
@@ -664,7 +664,7 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>-0.4389922286929491</v>
+        <v>-0.4389922286929457</v>
       </c>
       <c r="D4">
         <v>0.1872205247277714</v>
@@ -684,7 +684,7 @@
         <v>19</v>
       </c>
       <c r="C5">
-        <v>0.001191191498083018</v>
+        <v>0.001191191498083361</v>
       </c>
       <c r="D5">
         <v>9.83262566355898</v>
@@ -704,16 +704,16 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>-0.009307072647063453</v>
+        <v>-0.009307072647063593</v>
       </c>
       <c r="D6">
         <v>-4.660452729693743</v>
       </c>
       <c r="E6">
-        <v>0.04970611338492093</v>
+        <v>0.04966332233089334</v>
       </c>
       <c r="F6">
-        <v>7.888509312517782</v>
+        <v>7.881718243879401</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -724,16 +724,16 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>0.3880563903087753</v>
+        <v>0.388056390308776</v>
       </c>
       <c r="D7">
         <v>0.0512380896075415</v>
       </c>
       <c r="E7">
-        <v>-0.112298048605495</v>
+        <v>-0.1113651843188406</v>
       </c>
       <c r="F7">
-        <v>-17.82203720781681</v>
+        <v>-17.67398884695215</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -744,7 +744,7 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>-0.05356924416880902</v>
+        <v>-0.05356924416880983</v>
       </c>
       <c r="D8">
         <v>-0.09999999999999964</v>
@@ -764,16 +764,16 @@
         <v>23</v>
       </c>
       <c r="C9">
-        <v>-0.00330759214989478</v>
+        <v>-0.003307592149894438</v>
       </c>
       <c r="D9">
         <v>9.620048504446244</v>
       </c>
       <c r="E9">
-        <v>-0.02476890120154228</v>
+        <v>-0.02613611555466217</v>
       </c>
       <c r="F9">
-        <v>-3.930898927383719</v>
+        <v>-4.147879946871359</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -784,16 +784,16 @@
         <v>24</v>
       </c>
       <c r="C10">
-        <v>0.6675085002972716</v>
+        <v>0.6675085002972685</v>
       </c>
       <c r="D10">
         <v>0.814323332596989</v>
       </c>
       <c r="E10">
-        <v>0.5176938039653004</v>
+        <v>0.5209058585503092</v>
       </c>
       <c r="F10">
-        <v>82.15955977060796</v>
+        <v>82.66932246950591</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -804,7 +804,7 @@
         <v>25</v>
       </c>
       <c r="C11">
-        <v>0.07324169625436426</v>
+        <v>0.07324169625436268</v>
       </c>
       <c r="D11">
         <v>0.2408204503619338</v>
@@ -824,7 +824,7 @@
         <v>26</v>
       </c>
       <c r="C12">
-        <v>0.006780229674826145</v>
+        <v>0.006780229674825988</v>
       </c>
       <c r="D12">
         <v>0.1065715177314797</v>
@@ -844,7 +844,7 @@
         <v>27</v>
       </c>
       <c r="C13">
-        <v>0.005803592766630748</v>
+        <v>0.0058035927666311</v>
       </c>
       <c r="D13">
         <v>0.5040223775380159</v>
@@ -864,16 +864,16 @@
         <v>28</v>
       </c>
       <c r="C14">
-        <v>-0.01589706638059124</v>
+        <v>-0.01589706638059125</v>
       </c>
       <c r="D14">
         <v>2.102387948516338</v>
       </c>
       <c r="E14">
-        <v>-0.02178583610957874</v>
+        <v>-0.02234347650625441</v>
       </c>
       <c r="F14">
-        <v>-3.457477548094389</v>
+        <v>-3.54597675197193</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -884,7 +884,7 @@
         <v>29</v>
       </c>
       <c r="C15">
-        <v>-0.02980596643802811</v>
+        <v>-0.02980596643802884</v>
       </c>
       <c r="D15">
         <v>0.2254051079992214</v>
@@ -904,16 +904,16 @@
         <v>30</v>
       </c>
       <c r="C16">
-        <v>0.02687570203294232</v>
+        <v>0.0268757020329427</v>
       </c>
       <c r="D16">
         <v>-0.2907805015237463</v>
       </c>
       <c r="E16">
-        <v>-0.01204775542632242</v>
+        <v>-0.01162141624709692</v>
       </c>
       <c r="F16">
-        <v>-1.912014929421387</v>
+        <v>-1.844353622662937</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -924,7 +924,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>-0.04729568619617563</v>
+        <v>-0.04729568619617653</v>
       </c>
       <c r="D17">
         <v>-0.2820874471086032</v>
@@ -944,16 +944,16 @@
         <v>32</v>
       </c>
       <c r="C18">
-        <v>0.4350273589406671</v>
+        <v>0.4350273589406654</v>
       </c>
       <c r="D18">
         <v>0.280990491482469</v>
       </c>
       <c r="E18">
-        <v>0.04200897338481118</v>
+        <v>0.04216420745268946</v>
       </c>
       <c r="F18">
-        <v>6.666950103081809</v>
+        <v>6.691586215363866</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -964,7 +964,7 @@
         <v>33</v>
       </c>
       <c r="C19">
-        <v>-0.4998752122656598</v>
+        <v>-0.4998752122656581</v>
       </c>
       <c r="D19">
         <v>0.1611293778933875</v>
@@ -984,7 +984,7 @@
         <v>34</v>
       </c>
       <c r="C20">
-        <v>0.1732209292116763</v>
+        <v>0.1732209292116756</v>
       </c>
       <c r="D20">
         <v>0.1550488282042739</v>
@@ -1004,16 +1004,16 @@
         <v>35</v>
       </c>
       <c r="C21">
-        <v>-0.0002372484353651019</v>
+        <v>-0.0002372484353650417</v>
       </c>
       <c r="D21">
         <v>64</v>
       </c>
       <c r="E21">
-        <v>-0.01069679376731967</v>
+        <v>-0.01071175003644907</v>
       </c>
       <c r="F21">
-        <v>-1.697613261252926</v>
+        <v>-1.699986866034498</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1024,16 +1024,16 @@
         <v>36</v>
       </c>
       <c r="C22">
-        <v>-0.7165998496969331</v>
+        <v>-0.7165998496969285</v>
       </c>
       <c r="D22">
         <v>0.5493000000000023</v>
       </c>
       <c r="E22">
-        <v>-0.3994499422197237</v>
+        <v>-0.4025409526207778</v>
       </c>
       <c r="F22">
-        <v>-63.39390418002188</v>
+        <v>-63.88445680377235</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1044,7 +1044,7 @@
         <v>37</v>
       </c>
       <c r="C23">
-        <v>-0.1353699616787359</v>
+        <v>-0.135369961678736</v>
       </c>
       <c r="D23">
         <v>0.3504772148889446</v>
@@ -1064,7 +1064,7 @@
         <v>38</v>
       </c>
       <c r="C24">
-        <v>0.007251012986603225</v>
+        <v>0.007251012986603372</v>
       </c>
       <c r="D24">
         <v>-0.6702412868632712</v>
@@ -1084,7 +1084,7 @@
         <v>39</v>
       </c>
       <c r="C25">
-        <v>0.0006452571656390968</v>
+        <v>0.000645257165639065</v>
       </c>
       <c r="D25">
         <v>-4.7</v>
@@ -1104,16 +1104,16 @@
         <v>40</v>
       </c>
       <c r="C26">
-        <v>0.003313457911348319</v>
+        <v>0.003313457911348284</v>
       </c>
       <c r="D26">
         <v>-7</v>
       </c>
       <c r="E26">
-        <v>-0.04194318941729756</v>
+        <v>-0.04159606906204238</v>
       </c>
       <c r="F26">
-        <v>-6.656509990085508</v>
+        <v>-6.601420948353007</v>
       </c>
     </row>
   </sheetData>
@@ -1168,19 +1168,19 @@
         <v>43374</v>
       </c>
       <c r="B3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="C3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="D3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="E3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="F3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1194,7 +1194,7 @@
         <v>13741.17304740007</v>
       </c>
       <c r="D4">
-        <v>13706.44451029121</v>
+        <v>13706.4445102912</v>
       </c>
       <c r="E4">
         <v>13758.5373159545</v>
@@ -1234,7 +1234,7 @@
         <v>13767.77754031152</v>
       </c>
       <c r="D6">
-        <v>13517.55289119205</v>
+        <v>13517.55289119204</v>
       </c>
       <c r="E6">
         <v>13892.88986487126</v>
@@ -1257,10 +1257,10 @@
         <v>13535.47750966942</v>
       </c>
       <c r="E7">
-        <v>13869.49995631832</v>
+        <v>13869.49995631833</v>
       </c>
       <c r="F7">
-        <v>13702.48873299388</v>
+        <v>13702.48873299387</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1274,7 +1274,7 @@
         <v>13859.79940412151</v>
       </c>
       <c r="D8">
-        <v>13654.12261592925</v>
+        <v>13654.12261592924</v>
       </c>
       <c r="E8">
         <v>13962.63779821764</v>
@@ -1291,7 +1291,7 @@
         <v>13782.68435998989</v>
       </c>
       <c r="C9">
-        <v>13877.91802447373</v>
+        <v>13877.91802447374</v>
       </c>
       <c r="D9">
         <v>13687.45069550604</v>
@@ -1357,7 +1357,7 @@
         <v>13900.81387241998</v>
       </c>
       <c r="E12">
-        <v>14151.32063438864</v>
+        <v>14151.32063438865</v>
       </c>
       <c r="F12">
         <v>14026.06725340431</v>
@@ -1397,7 +1397,7 @@
         <v>13913.9463585324</v>
       </c>
       <c r="E14">
-        <v>14159.02565105452</v>
+        <v>14159.02565105453</v>
       </c>
       <c r="F14">
         <v>14036.48600479346</v>
@@ -1454,10 +1454,10 @@
         <v>14185.60080772286</v>
       </c>
       <c r="D17">
-        <v>14032.72420708164</v>
+        <v>14032.72420708165</v>
       </c>
       <c r="E17">
-        <v>14262.03910804346</v>
+        <v>14262.03910804347</v>
       </c>
       <c r="F17">
         <v>14147.38165756256</v>
@@ -1477,10 +1477,10 @@
         <v>14060.36668538631</v>
       </c>
       <c r="E18">
-        <v>14282.26934594421</v>
+        <v>14282.26934594422</v>
       </c>
       <c r="F18">
-        <v>14171.31801566526</v>
+        <v>14171.31801566527</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1528,19 +1528,19 @@
         <v>43922</v>
       </c>
       <c r="B21">
-        <v>10854.56980066336</v>
+        <v>10854.56980066337</v>
       </c>
       <c r="C21">
         <v>11148.33032430996</v>
       </c>
       <c r="D21">
-        <v>10560.80927701677</v>
+        <v>10560.80927701678</v>
       </c>
       <c r="E21">
         <v>11442.09084795655</v>
       </c>
       <c r="F21">
-        <v>11001.45006248666</v>
+        <v>11001.45006248667</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1548,19 +1548,19 @@
         <v>43952</v>
       </c>
       <c r="B22">
-        <v>12568.97916809153</v>
+        <v>12568.97916809154</v>
       </c>
       <c r="C22">
-        <v>12985.86644559765</v>
+        <v>12985.86644559766</v>
       </c>
       <c r="D22">
-        <v>12152.09189058541</v>
+        <v>12152.09189058542</v>
       </c>
       <c r="E22">
-        <v>13402.75372310377</v>
+        <v>13402.75372310378</v>
       </c>
       <c r="F22">
-        <v>12777.42280684459</v>
+        <v>12777.4228068446</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1574,7 +1574,7 @@
         <v>13747.30149729845</v>
       </c>
       <c r="D23">
-        <v>12867.31279217293</v>
+        <v>12867.31279217294</v>
       </c>
       <c r="E23">
         <v>14187.2958498612</v>
@@ -1588,19 +1588,19 @@
         <v>44013</v>
       </c>
       <c r="B24">
-        <v>13497.45617730901</v>
+        <v>13497.45617730902</v>
       </c>
       <c r="C24">
         <v>13951.34004731577</v>
       </c>
       <c r="D24">
-        <v>13043.57230730226</v>
+        <v>13043.57230730227</v>
       </c>
       <c r="E24">
         <v>14405.22391732253</v>
       </c>
       <c r="F24">
-        <v>13724.39811231239</v>
+        <v>13724.3981123124</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1628,7 +1628,7 @@
         <v>44075</v>
       </c>
       <c r="B26">
-        <v>13654.8981252881</v>
+        <v>13654.89812528809</v>
       </c>
       <c r="C26">
         <v>14098.68235471921</v>
@@ -1697,7 +1697,7 @@
         <v>13372.70227113109</v>
       </c>
       <c r="E29">
-        <v>14647.07207424863</v>
+        <v>14647.07207424862</v>
       </c>
       <c r="F29">
         <v>14009.88717268986</v>
@@ -1708,7 +1708,7 @@
         <v>44197</v>
       </c>
       <c r="B30">
-        <v>14061.27893287306</v>
+        <v>14061.27893287305</v>
       </c>
       <c r="C30">
         <v>14479.6952506427</v>
@@ -1731,10 +1731,10 @@
         <v>13784.36429499859</v>
       </c>
       <c r="C31">
-        <v>14201.52960045673</v>
+        <v>14201.52960045674</v>
       </c>
       <c r="D31">
-        <v>13367.19898954044</v>
+        <v>13367.19898954045</v>
       </c>
       <c r="E31">
         <v>14618.69490591488</v>
@@ -1857,10 +1857,10 @@
         <v>14211.72731105986</v>
       </c>
       <c r="E37">
-        <v>15404.92067152225</v>
+        <v>15404.92067152224</v>
       </c>
       <c r="F37">
-        <v>14808.32399129106</v>
+        <v>14808.32399129105</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1871,7 +1871,7 @@
         <v>14668.00240962889</v>
       </c>
       <c r="C38">
-        <v>15062.63364801735</v>
+        <v>15062.63364801736</v>
       </c>
       <c r="D38">
         <v>14273.37117124043</v>
@@ -1880,7 +1880,7 @@
         <v>15457.26488640582</v>
       </c>
       <c r="F38">
-        <v>14865.31802882312</v>
+        <v>14865.31802882313</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1894,7 +1894,7 @@
         <v>15226.00953257467</v>
       </c>
       <c r="D39">
-        <v>14445.46421436111</v>
+        <v>14445.46421436112</v>
       </c>
       <c r="E39">
         <v>15616.28219168145</v>
@@ -1914,7 +1914,7 @@
         <v>15240.16450376901</v>
       </c>
       <c r="D40">
-        <v>14464.93215988632</v>
+        <v>14464.93215988633</v>
       </c>
       <c r="E40">
         <v>15627.78067571035</v>
@@ -1931,10 +1931,10 @@
         <v>14727.70483417406</v>
       </c>
       <c r="C41">
-        <v>15110.81509093609</v>
+        <v>15110.81509093608</v>
       </c>
       <c r="D41">
-        <v>14344.59457741204</v>
+        <v>14344.59457741203</v>
       </c>
       <c r="E41">
         <v>15493.92534769811</v>
@@ -1948,7 +1948,7 @@
         <v>44562</v>
       </c>
       <c r="B42">
-        <v>14881.71172824103</v>
+        <v>14881.71172824104</v>
       </c>
       <c r="C42">
         <v>15259.06409298531</v>
@@ -1974,7 +1974,7 @@
         <v>15245.70189424054</v>
       </c>
       <c r="D43">
-        <v>14498.05903351751</v>
+        <v>14498.05903351752</v>
       </c>
       <c r="E43">
         <v>15619.52332460205</v>
@@ -2014,7 +2014,7 @@
         <v>15293.24271369473</v>
       </c>
       <c r="D45">
-        <v>14558.56059352317</v>
+        <v>14558.56059352318</v>
       </c>
       <c r="E45">
         <v>15660.5837737805</v>
@@ -2057,7 +2057,7 @@
         <v>14547.16165161462</v>
       </c>
       <c r="E47">
-        <v>15625.84500381681</v>
+        <v>15625.8450038168</v>
       </c>
       <c r="F47">
         <v>15086.50332771571</v>
@@ -2077,10 +2077,10 @@
         <v>14510.69195230835</v>
       </c>
       <c r="E48">
-        <v>15577.78131335764</v>
+        <v>15577.78131335763</v>
       </c>
       <c r="F48">
-        <v>15044.236632833</v>
+        <v>15044.23663283299</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2094,7 +2094,7 @@
         <v>15298.49419773592</v>
       </c>
       <c r="D49">
-        <v>14594.43606838795</v>
+        <v>14594.43606838796</v>
       </c>
       <c r="E49">
         <v>15650.5232624099</v>
@@ -2108,19 +2108,19 @@
         <v>44805</v>
       </c>
       <c r="B50">
-        <v>14987.51193641546</v>
+        <v>14987.51193641545</v>
       </c>
       <c r="C50">
-        <v>15337.3904175255</v>
+        <v>15337.39041752549</v>
       </c>
       <c r="D50">
-        <v>14637.63345530542</v>
+        <v>14637.63345530541</v>
       </c>
       <c r="E50">
         <v>15687.26889863554</v>
       </c>
       <c r="F50">
-        <v>15162.45117697048</v>
+        <v>15162.45117697047</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2134,13 +2134,13 @@
         <v>15433.60441261612</v>
       </c>
       <c r="D51">
-        <v>14739.20592552061</v>
+        <v>14739.20592552062</v>
       </c>
       <c r="E51">
         <v>15780.80365616387</v>
       </c>
       <c r="F51">
-        <v>15260.00479084224</v>
+        <v>15260.00479084225</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2157,7 +2157,7 @@
         <v>14637.86697723937</v>
       </c>
       <c r="E52">
-        <v>15671.4001378396</v>
+        <v>15671.40013783959</v>
       </c>
       <c r="F52">
         <v>15154.63355753948</v>
@@ -2217,10 +2217,10 @@
         <v>14770.22126653674</v>
       </c>
       <c r="E55">
-        <v>15788.25350869447</v>
+        <v>15788.25350869446</v>
       </c>
       <c r="F55">
-        <v>15279.23738761561</v>
+        <v>15279.2373876156</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2231,7 +2231,7 @@
         <v>15137.0722547488</v>
       </c>
       <c r="C56">
-        <v>15473.71508568345</v>
+        <v>15473.71508568344</v>
       </c>
       <c r="D56">
         <v>14800.42942381416</v>
@@ -2271,7 +2271,7 @@
         <v>15184.83278932868</v>
       </c>
       <c r="C58">
-        <v>15515.25841688104</v>
+        <v>15515.25841688105</v>
       </c>
       <c r="D58">
         <v>14854.40716177632</v>
@@ -2320,7 +2320,7 @@
         <v>15923.74868623471</v>
       </c>
       <c r="F60">
-        <v>15434.91718733836</v>
+        <v>15434.91718733837</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2331,10 +2331,10 @@
         <v>15375.36526397869</v>
       </c>
       <c r="C61">
-        <v>15699.99966360649</v>
+        <v>15699.99966360648</v>
       </c>
       <c r="D61">
-        <v>15050.73086435088</v>
+        <v>15050.73086435089</v>
       </c>
       <c r="E61">
         <v>16024.63406323429</v>
@@ -2354,7 +2354,7 @@
         <v>15661.02423338759</v>
       </c>
       <c r="D62">
-        <v>15016.01051814424</v>
+        <v>15016.01051814423</v>
       </c>
       <c r="E62">
         <v>15983.53109100927</v>
@@ -2388,19 +2388,19 @@
         <v>45231</v>
       </c>
       <c r="B64">
-        <v>15424.48851596082</v>
+        <v>15424.48851596081</v>
       </c>
       <c r="C64">
-        <v>15743.48310645482</v>
+        <v>15743.48310645481</v>
       </c>
       <c r="D64">
-        <v>15105.49392546681</v>
+        <v>15105.4939254668</v>
       </c>
       <c r="E64">
-        <v>16062.47769694883</v>
+        <v>16062.47769694882</v>
       </c>
       <c r="F64">
-        <v>15583.98581120782</v>
+        <v>15583.98581120781</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2431,7 +2431,7 @@
         <v>15421.94607126623</v>
       </c>
       <c r="C66">
-        <v>15738.7757349296</v>
+        <v>15738.77573492959</v>
       </c>
       <c r="D66">
         <v>15105.11640760285</v>
@@ -2488,7 +2488,7 @@
         <v>45383</v>
       </c>
       <c r="B69">
-        <v>15538.6849324647</v>
+        <v>15538.68493246469</v>
       </c>
       <c r="C69">
         <v>15849.13020162564</v>
@@ -2534,7 +2534,7 @@
         <v>15918.09554088757</v>
       </c>
       <c r="D71">
-        <v>15303.16298787397</v>
+        <v>15303.16298787398</v>
       </c>
       <c r="E71">
         <v>16225.56181739436</v>
@@ -2560,7 +2560,7 @@
         <v>16332.35260203241</v>
       </c>
       <c r="F72">
-        <v>15872.88007831158</v>
+        <v>15872.88007831159</v>
       </c>
     </row>
   </sheetData>
@@ -5064,7 +5064,7 @@
         <v>43374</v>
       </c>
       <c r="B227">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="C227">
         <v>13727.1</v>
@@ -5108,7 +5108,7 @@
         <v>43497</v>
       </c>
       <c r="B231">
-        <v>13702.48873299388</v>
+        <v>13702.48873299387</v>
       </c>
       <c r="C231">
         <v>13723.1</v>
@@ -5229,7 +5229,7 @@
         <v>43831</v>
       </c>
       <c r="B242">
-        <v>14171.31801566526</v>
+        <v>14171.31801566527</v>
       </c>
       <c r="C242">
         <v>14184.79999999999</v>
@@ -5262,7 +5262,7 @@
         <v>43922</v>
       </c>
       <c r="B245">
-        <v>11001.45006248666</v>
+        <v>11001.45006248667</v>
       </c>
       <c r="C245">
         <v>11783.29999999999</v>
@@ -5273,7 +5273,7 @@
         <v>43952</v>
       </c>
       <c r="B246">
-        <v>12777.42280684459</v>
+        <v>12777.4228068446</v>
       </c>
       <c r="C246">
         <v>12757.99999999999</v>
@@ -5295,7 +5295,7 @@
         <v>44013</v>
       </c>
       <c r="B248">
-        <v>13724.39811231239</v>
+        <v>13724.3981123124</v>
       </c>
       <c r="C248">
         <v>13667.29999999999</v>
@@ -5438,7 +5438,7 @@
         <v>44409</v>
       </c>
       <c r="B261">
-        <v>14808.32399129106</v>
+        <v>14808.32399129105</v>
       </c>
       <c r="C261">
         <v>14863</v>
@@ -5449,7 +5449,7 @@
         <v>44440</v>
       </c>
       <c r="B262">
-        <v>14865.31802882312</v>
+        <v>14865.31802882313</v>
       </c>
       <c r="C262">
         <v>14899.4</v>
@@ -5559,7 +5559,7 @@
         <v>44743</v>
       </c>
       <c r="B272">
-        <v>15044.236632833</v>
+        <v>15044.23663283299</v>
       </c>
       <c r="C272">
         <v>15069.1</v>
@@ -5581,7 +5581,7 @@
         <v>44805</v>
       </c>
       <c r="B274">
-        <v>15162.45117697048</v>
+        <v>15162.45117697047</v>
       </c>
       <c r="C274">
         <v>15176.7</v>
@@ -5592,7 +5592,7 @@
         <v>44835</v>
       </c>
       <c r="B275">
-        <v>15260.00479084224</v>
+        <v>15260.00479084225</v>
       </c>
       <c r="C275">
         <v>15202.7</v>
@@ -5636,7 +5636,7 @@
         <v>44958</v>
       </c>
       <c r="B279">
-        <v>15279.23738761561</v>
+        <v>15279.2373876156</v>
       </c>
       <c r="C279">
         <v>15325.5</v>
@@ -5691,7 +5691,7 @@
         <v>45108</v>
       </c>
       <c r="B284">
-        <v>15434.91718733836</v>
+        <v>15434.91718733837</v>
       </c>
       <c r="C284">
         <v>15448.3</v>
@@ -5735,7 +5735,7 @@
         <v>45231</v>
       </c>
       <c r="B288">
-        <v>15583.98581120782</v>
+        <v>15583.98581120781</v>
       </c>
       <c r="C288">
         <v>15584.29999999999</v>
@@ -5823,7 +5823,7 @@
         <v>45474</v>
       </c>
       <c r="B296">
-        <v>15872.88007831158</v>
+        <v>15872.88007831159</v>
       </c>
       <c r="C296">
         <v>15870.29999999999</v>

--- a/app/analytical-backend/data/07_model_output/ml.xlsx
+++ b/app/analytical-backend/data/07_model_output/ml.xlsx
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.0009867029955283868</v>
+        <v>0.0009867029955283994</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -578,7 +578,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>64.34236092160945</v>
+        <v>64.3423609216093</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>288</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -624,7 +624,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0001726251966894671</v>
+        <v>0.0001726251966894652</v>
       </c>
       <c r="D2">
         <v>142</v>
@@ -644,7 +644,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>-4.396177626687803E-05</v>
+        <v>-4.396177626689313E-05</v>
       </c>
       <c r="D3">
         <v>-237</v>
@@ -664,7 +664,7 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>-0.4389922286929491</v>
+        <v>-0.4389922286929457</v>
       </c>
       <c r="D4">
         <v>0.1872205247277714</v>
@@ -684,7 +684,7 @@
         <v>19</v>
       </c>
       <c r="C5">
-        <v>0.001191191498083018</v>
+        <v>0.001191191498083361</v>
       </c>
       <c r="D5">
         <v>9.83262566355898</v>
@@ -704,16 +704,16 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>-0.009307072647063453</v>
+        <v>-0.009307072647063593</v>
       </c>
       <c r="D6">
         <v>-4.660452729693743</v>
       </c>
       <c r="E6">
-        <v>0.04970611338492093</v>
+        <v>0.05251545082554838</v>
       </c>
       <c r="F6">
-        <v>7.888509312517782</v>
+        <v>8.334359592366615</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -724,16 +724,16 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>0.3880563903087753</v>
+        <v>0.388056390308776</v>
       </c>
       <c r="D7">
         <v>0.0512380896075415</v>
       </c>
       <c r="E7">
-        <v>-0.112298048605495</v>
+        <v>-0.113368907531457</v>
       </c>
       <c r="F7">
-        <v>-17.82203720781681</v>
+        <v>-17.99198573196398</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -744,7 +744,7 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>-0.05356924416880902</v>
+        <v>-0.05356924416880983</v>
       </c>
       <c r="D8">
         <v>-0.09999999999999964</v>
@@ -764,16 +764,16 @@
         <v>23</v>
       </c>
       <c r="C9">
-        <v>-0.00330759214989478</v>
+        <v>-0.003307592149894438</v>
       </c>
       <c r="D9">
         <v>9.620048504446244</v>
       </c>
       <c r="E9">
-        <v>-0.02476890120154228</v>
+        <v>-0.02639966617130927</v>
       </c>
       <c r="F9">
-        <v>-3.930898927383719</v>
+        <v>-4.1897062203851</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -784,16 +784,16 @@
         <v>24</v>
       </c>
       <c r="C10">
-        <v>0.6675085002972716</v>
+        <v>0.6675085002972685</v>
       </c>
       <c r="D10">
         <v>0.814323332596989</v>
       </c>
       <c r="E10">
-        <v>0.5176938039653004</v>
+        <v>0.5174690044956594</v>
       </c>
       <c r="F10">
-        <v>82.15955977060796</v>
+        <v>82.12388342047079</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -804,7 +804,7 @@
         <v>25</v>
       </c>
       <c r="C11">
-        <v>0.07324169625436426</v>
+        <v>0.07324169625436268</v>
       </c>
       <c r="D11">
         <v>0.2408204503619338</v>
@@ -824,7 +824,7 @@
         <v>26</v>
       </c>
       <c r="C12">
-        <v>0.006780229674826145</v>
+        <v>0.006780229674825988</v>
       </c>
       <c r="D12">
         <v>0.1065715177314797</v>
@@ -844,7 +844,7 @@
         <v>27</v>
       </c>
       <c r="C13">
-        <v>0.005803592766630748</v>
+        <v>0.0058035927666311</v>
       </c>
       <c r="D13">
         <v>0.5040223775380159</v>
@@ -864,16 +864,16 @@
         <v>28</v>
       </c>
       <c r="C14">
-        <v>-0.01589706638059124</v>
+        <v>-0.01589706638059125</v>
       </c>
       <c r="D14">
         <v>2.102387948516338</v>
       </c>
       <c r="E14">
-        <v>-0.02178583610957874</v>
+        <v>-0.02092405754781741</v>
       </c>
       <c r="F14">
-        <v>-3.457477548094389</v>
+        <v>-3.32071070501111</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -884,7 +884,7 @@
         <v>29</v>
       </c>
       <c r="C15">
-        <v>-0.02980596643802811</v>
+        <v>-0.02980596643802884</v>
       </c>
       <c r="D15">
         <v>0.2254051079992214</v>
@@ -904,16 +904,16 @@
         <v>30</v>
       </c>
       <c r="C16">
-        <v>0.02687570203294232</v>
+        <v>0.0268757020329427</v>
       </c>
       <c r="D16">
         <v>-0.2907805015237463</v>
       </c>
       <c r="E16">
-        <v>-0.01204775542632242</v>
+        <v>-0.0132127086466758</v>
       </c>
       <c r="F16">
-        <v>-1.912014929421387</v>
+        <v>-2.096896500353291</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -924,7 +924,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>-0.04729568619617563</v>
+        <v>-0.04729568619617653</v>
       </c>
       <c r="D17">
         <v>-0.2820874471086032</v>
@@ -944,16 +944,16 @@
         <v>32</v>
       </c>
       <c r="C18">
-        <v>0.4350273589406671</v>
+        <v>0.4350273589406654</v>
       </c>
       <c r="D18">
         <v>0.280990491482469</v>
       </c>
       <c r="E18">
-        <v>0.04200897338481118</v>
+        <v>0.04134731252167591</v>
       </c>
       <c r="F18">
-        <v>6.666950103081809</v>
+        <v>6.561942539127226</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -964,7 +964,7 @@
         <v>33</v>
       </c>
       <c r="C19">
-        <v>-0.4998752122656598</v>
+        <v>-0.4998752122656581</v>
       </c>
       <c r="D19">
         <v>0.1611293778933875</v>
@@ -984,7 +984,7 @@
         <v>34</v>
       </c>
       <c r="C20">
-        <v>0.1732209292116763</v>
+        <v>0.1732209292116756</v>
       </c>
       <c r="D20">
         <v>0.1550488282042739</v>
@@ -1004,16 +1004,16 @@
         <v>35</v>
       </c>
       <c r="C21">
-        <v>-0.0002372484353651019</v>
+        <v>-0.0002372484353650417</v>
       </c>
       <c r="D21">
         <v>64</v>
       </c>
       <c r="E21">
-        <v>-0.01069679376731967</v>
+        <v>-0.009398522163904265</v>
       </c>
       <c r="F21">
-        <v>-1.697613261252926</v>
+        <v>-1.491573662978029</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1024,16 +1024,16 @@
         <v>36</v>
       </c>
       <c r="C22">
-        <v>-0.7165998496969331</v>
+        <v>-0.7165998496969285</v>
       </c>
       <c r="D22">
         <v>0.5493000000000023</v>
       </c>
       <c r="E22">
-        <v>-0.3994499422197237</v>
+        <v>-0.4014978482502735</v>
       </c>
       <c r="F22">
-        <v>-63.39390418002188</v>
+        <v>-63.71891301086018</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1044,7 +1044,7 @@
         <v>37</v>
       </c>
       <c r="C23">
-        <v>-0.1353699616787359</v>
+        <v>-0.135369961678736</v>
       </c>
       <c r="D23">
         <v>0.3504772148889446</v>
@@ -1064,7 +1064,7 @@
         <v>38</v>
       </c>
       <c r="C24">
-        <v>0.007251012986603225</v>
+        <v>0.007251012986603372</v>
       </c>
       <c r="D24">
         <v>-0.6702412868632712</v>
@@ -1084,7 +1084,7 @@
         <v>39</v>
       </c>
       <c r="C25">
-        <v>0.0006452571656390968</v>
+        <v>0.000645257165639065</v>
       </c>
       <c r="D25">
         <v>-4.7</v>
@@ -1104,16 +1104,16 @@
         <v>40</v>
       </c>
       <c r="C26">
-        <v>0.003313457911348319</v>
+        <v>0.003313457911348284</v>
       </c>
       <c r="D26">
         <v>-7</v>
       </c>
       <c r="E26">
-        <v>-0.04194318941729756</v>
+        <v>-0.04011163354367775</v>
       </c>
       <c r="F26">
-        <v>-6.656509990085508</v>
+        <v>-6.365836578281993</v>
       </c>
     </row>
   </sheetData>
@@ -1168,19 +1168,19 @@
         <v>43374</v>
       </c>
       <c r="B3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="C3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="D3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="E3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="F3">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1194,7 +1194,7 @@
         <v>13741.17304740007</v>
       </c>
       <c r="D4">
-        <v>13706.44451029121</v>
+        <v>13706.4445102912</v>
       </c>
       <c r="E4">
         <v>13758.5373159545</v>
@@ -1234,7 +1234,7 @@
         <v>13767.77754031152</v>
       </c>
       <c r="D6">
-        <v>13517.55289119205</v>
+        <v>13517.55289119204</v>
       </c>
       <c r="E6">
         <v>13892.88986487126</v>
@@ -1257,10 +1257,10 @@
         <v>13535.47750966942</v>
       </c>
       <c r="E7">
-        <v>13869.49995631832</v>
+        <v>13869.49995631833</v>
       </c>
       <c r="F7">
-        <v>13702.48873299388</v>
+        <v>13702.48873299387</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1274,7 +1274,7 @@
         <v>13859.79940412151</v>
       </c>
       <c r="D8">
-        <v>13654.12261592925</v>
+        <v>13654.12261592924</v>
       </c>
       <c r="E8">
         <v>13962.63779821764</v>
@@ -1291,7 +1291,7 @@
         <v>13782.68435998989</v>
       </c>
       <c r="C9">
-        <v>13877.91802447373</v>
+        <v>13877.91802447374</v>
       </c>
       <c r="D9">
         <v>13687.45069550604</v>
@@ -1357,7 +1357,7 @@
         <v>13900.81387241998</v>
       </c>
       <c r="E12">
-        <v>14151.32063438864</v>
+        <v>14151.32063438865</v>
       </c>
       <c r="F12">
         <v>14026.06725340431</v>
@@ -1397,7 +1397,7 @@
         <v>13913.9463585324</v>
       </c>
       <c r="E14">
-        <v>14159.02565105452</v>
+        <v>14159.02565105453</v>
       </c>
       <c r="F14">
         <v>14036.48600479346</v>
@@ -1454,10 +1454,10 @@
         <v>14185.60080772286</v>
       </c>
       <c r="D17">
-        <v>14032.72420708164</v>
+        <v>14032.72420708165</v>
       </c>
       <c r="E17">
-        <v>14262.03910804346</v>
+        <v>14262.03910804347</v>
       </c>
       <c r="F17">
         <v>14147.38165756256</v>
@@ -1477,10 +1477,10 @@
         <v>14060.36668538631</v>
       </c>
       <c r="E18">
-        <v>14282.26934594421</v>
+        <v>14282.26934594422</v>
       </c>
       <c r="F18">
-        <v>14171.31801566526</v>
+        <v>14171.31801566527</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1528,19 +1528,19 @@
         <v>43922</v>
       </c>
       <c r="B21">
-        <v>10854.56980066336</v>
+        <v>10854.56980066337</v>
       </c>
       <c r="C21">
         <v>11148.33032430996</v>
       </c>
       <c r="D21">
-        <v>10560.80927701677</v>
+        <v>10560.80927701678</v>
       </c>
       <c r="E21">
         <v>11442.09084795655</v>
       </c>
       <c r="F21">
-        <v>11001.45006248666</v>
+        <v>11001.45006248667</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1548,19 +1548,19 @@
         <v>43952</v>
       </c>
       <c r="B22">
-        <v>12568.97916809153</v>
+        <v>12568.97916809154</v>
       </c>
       <c r="C22">
-        <v>12985.86644559765</v>
+        <v>12985.86644559766</v>
       </c>
       <c r="D22">
-        <v>12152.09189058541</v>
+        <v>12152.09189058542</v>
       </c>
       <c r="E22">
-        <v>13402.75372310377</v>
+        <v>13402.75372310378</v>
       </c>
       <c r="F22">
-        <v>12777.42280684459</v>
+        <v>12777.4228068446</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1574,7 +1574,7 @@
         <v>13747.30149729845</v>
       </c>
       <c r="D23">
-        <v>12867.31279217293</v>
+        <v>12867.31279217294</v>
       </c>
       <c r="E23">
         <v>14187.2958498612</v>
@@ -1588,19 +1588,19 @@
         <v>44013</v>
       </c>
       <c r="B24">
-        <v>13497.45617730901</v>
+        <v>13497.45617730902</v>
       </c>
       <c r="C24">
         <v>13951.34004731577</v>
       </c>
       <c r="D24">
-        <v>13043.57230730226</v>
+        <v>13043.57230730227</v>
       </c>
       <c r="E24">
         <v>14405.22391732253</v>
       </c>
       <c r="F24">
-        <v>13724.39811231239</v>
+        <v>13724.3981123124</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1628,7 +1628,7 @@
         <v>44075</v>
       </c>
       <c r="B26">
-        <v>13654.8981252881</v>
+        <v>13654.89812528809</v>
       </c>
       <c r="C26">
         <v>14098.68235471921</v>
@@ -1697,7 +1697,7 @@
         <v>13372.70227113109</v>
       </c>
       <c r="E29">
-        <v>14647.07207424863</v>
+        <v>14647.07207424862</v>
       </c>
       <c r="F29">
         <v>14009.88717268986</v>
@@ -1708,7 +1708,7 @@
         <v>44197</v>
       </c>
       <c r="B30">
-        <v>14061.27893287306</v>
+        <v>14061.27893287305</v>
       </c>
       <c r="C30">
         <v>14479.6952506427</v>
@@ -1731,10 +1731,10 @@
         <v>13784.36429499859</v>
       </c>
       <c r="C31">
-        <v>14201.52960045673</v>
+        <v>14201.52960045674</v>
       </c>
       <c r="D31">
-        <v>13367.19898954044</v>
+        <v>13367.19898954045</v>
       </c>
       <c r="E31">
         <v>14618.69490591488</v>
@@ -1857,10 +1857,10 @@
         <v>14211.72731105986</v>
       </c>
       <c r="E37">
-        <v>15404.92067152225</v>
+        <v>15404.92067152224</v>
       </c>
       <c r="F37">
-        <v>14808.32399129106</v>
+        <v>14808.32399129105</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1871,7 +1871,7 @@
         <v>14668.00240962889</v>
       </c>
       <c r="C38">
-        <v>15062.63364801735</v>
+        <v>15062.63364801736</v>
       </c>
       <c r="D38">
         <v>14273.37117124043</v>
@@ -1880,7 +1880,7 @@
         <v>15457.26488640582</v>
       </c>
       <c r="F38">
-        <v>14865.31802882312</v>
+        <v>14865.31802882313</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1894,7 +1894,7 @@
         <v>15226.00953257467</v>
       </c>
       <c r="D39">
-        <v>14445.46421436111</v>
+        <v>14445.46421436112</v>
       </c>
       <c r="E39">
         <v>15616.28219168145</v>
@@ -1914,7 +1914,7 @@
         <v>15240.16450376901</v>
       </c>
       <c r="D40">
-        <v>14464.93215988632</v>
+        <v>14464.93215988633</v>
       </c>
       <c r="E40">
         <v>15627.78067571035</v>
@@ -1931,10 +1931,10 @@
         <v>14727.70483417406</v>
       </c>
       <c r="C41">
-        <v>15110.81509093609</v>
+        <v>15110.81509093608</v>
       </c>
       <c r="D41">
-        <v>14344.59457741204</v>
+        <v>14344.59457741203</v>
       </c>
       <c r="E41">
         <v>15493.92534769811</v>
@@ -1948,7 +1948,7 @@
         <v>44562</v>
       </c>
       <c r="B42">
-        <v>14881.71172824103</v>
+        <v>14881.71172824104</v>
       </c>
       <c r="C42">
         <v>15259.06409298531</v>
@@ -1974,7 +1974,7 @@
         <v>15245.70189424054</v>
       </c>
       <c r="D43">
-        <v>14498.05903351751</v>
+        <v>14498.05903351752</v>
       </c>
       <c r="E43">
         <v>15619.52332460205</v>
@@ -2014,7 +2014,7 @@
         <v>15293.24271369473</v>
       </c>
       <c r="D45">
-        <v>14558.56059352317</v>
+        <v>14558.56059352318</v>
       </c>
       <c r="E45">
         <v>15660.5837737805</v>
@@ -2057,7 +2057,7 @@
         <v>14547.16165161462</v>
       </c>
       <c r="E47">
-        <v>15625.84500381681</v>
+        <v>15625.8450038168</v>
       </c>
       <c r="F47">
         <v>15086.50332771571</v>
@@ -2077,10 +2077,10 @@
         <v>14510.69195230835</v>
       </c>
       <c r="E48">
-        <v>15577.78131335764</v>
+        <v>15577.78131335763</v>
       </c>
       <c r="F48">
-        <v>15044.236632833</v>
+        <v>15044.23663283299</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2094,7 +2094,7 @@
         <v>15298.49419773592</v>
       </c>
       <c r="D49">
-        <v>14594.43606838795</v>
+        <v>14594.43606838796</v>
       </c>
       <c r="E49">
         <v>15650.5232624099</v>
@@ -2108,19 +2108,19 @@
         <v>44805</v>
       </c>
       <c r="B50">
-        <v>14987.51193641546</v>
+        <v>14987.51193641545</v>
       </c>
       <c r="C50">
-        <v>15337.3904175255</v>
+        <v>15337.39041752549</v>
       </c>
       <c r="D50">
-        <v>14637.63345530542</v>
+        <v>14637.63345530541</v>
       </c>
       <c r="E50">
         <v>15687.26889863554</v>
       </c>
       <c r="F50">
-        <v>15162.45117697048</v>
+        <v>15162.45117697047</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2134,13 +2134,13 @@
         <v>15433.60441261612</v>
       </c>
       <c r="D51">
-        <v>14739.20592552061</v>
+        <v>14739.20592552062</v>
       </c>
       <c r="E51">
         <v>15780.80365616387</v>
       </c>
       <c r="F51">
-        <v>15260.00479084224</v>
+        <v>15260.00479084225</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2157,7 +2157,7 @@
         <v>14637.86697723937</v>
       </c>
       <c r="E52">
-        <v>15671.4001378396</v>
+        <v>15671.40013783959</v>
       </c>
       <c r="F52">
         <v>15154.63355753948</v>
@@ -2217,10 +2217,10 @@
         <v>14770.22126653674</v>
       </c>
       <c r="E55">
-        <v>15788.25350869447</v>
+        <v>15788.25350869446</v>
       </c>
       <c r="F55">
-        <v>15279.23738761561</v>
+        <v>15279.2373876156</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2231,7 +2231,7 @@
         <v>15137.0722547488</v>
       </c>
       <c r="C56">
-        <v>15473.71508568345</v>
+        <v>15473.71508568344</v>
       </c>
       <c r="D56">
         <v>14800.42942381416</v>
@@ -2271,7 +2271,7 @@
         <v>15184.83278932868</v>
       </c>
       <c r="C58">
-        <v>15515.25841688104</v>
+        <v>15515.25841688105</v>
       </c>
       <c r="D58">
         <v>14854.40716177632</v>
@@ -2320,7 +2320,7 @@
         <v>15923.74868623471</v>
       </c>
       <c r="F60">
-        <v>15434.91718733836</v>
+        <v>15434.91718733837</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2331,10 +2331,10 @@
         <v>15375.36526397869</v>
       </c>
       <c r="C61">
-        <v>15699.99966360649</v>
+        <v>15699.99966360648</v>
       </c>
       <c r="D61">
-        <v>15050.73086435088</v>
+        <v>15050.73086435089</v>
       </c>
       <c r="E61">
         <v>16024.63406323429</v>
@@ -2354,7 +2354,7 @@
         <v>15661.02423338759</v>
       </c>
       <c r="D62">
-        <v>15016.01051814424</v>
+        <v>15016.01051814423</v>
       </c>
       <c r="E62">
         <v>15983.53109100927</v>
@@ -2388,19 +2388,19 @@
         <v>45231</v>
       </c>
       <c r="B64">
-        <v>15424.48851596082</v>
+        <v>15424.48851596081</v>
       </c>
       <c r="C64">
-        <v>15743.48310645482</v>
+        <v>15743.48310645481</v>
       </c>
       <c r="D64">
-        <v>15105.49392546681</v>
+        <v>15105.4939254668</v>
       </c>
       <c r="E64">
-        <v>16062.47769694883</v>
+        <v>16062.47769694882</v>
       </c>
       <c r="F64">
-        <v>15583.98581120782</v>
+        <v>15583.98581120781</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2431,7 +2431,7 @@
         <v>15421.94607126623</v>
       </c>
       <c r="C66">
-        <v>15738.7757349296</v>
+        <v>15738.77573492959</v>
       </c>
       <c r="D66">
         <v>15105.11640760285</v>
@@ -2488,7 +2488,7 @@
         <v>45383</v>
       </c>
       <c r="B69">
-        <v>15538.6849324647</v>
+        <v>15538.68493246469</v>
       </c>
       <c r="C69">
         <v>15849.13020162564</v>
@@ -2534,7 +2534,7 @@
         <v>15918.09554088757</v>
       </c>
       <c r="D71">
-        <v>15303.16298787397</v>
+        <v>15303.16298787398</v>
       </c>
       <c r="E71">
         <v>16225.56181739436</v>
@@ -2560,7 +2560,7 @@
         <v>16332.35260203241</v>
       </c>
       <c r="F72">
-        <v>15872.88007831158</v>
+        <v>15872.88007831159</v>
       </c>
     </row>
   </sheetData>
@@ -5064,7 +5064,7 @@
         <v>43374</v>
       </c>
       <c r="B227">
-        <v>13745.05884723892</v>
+        <v>13745.05884723891</v>
       </c>
       <c r="C227">
         <v>13727.1</v>
@@ -5108,7 +5108,7 @@
         <v>43497</v>
       </c>
       <c r="B231">
-        <v>13702.48873299388</v>
+        <v>13702.48873299387</v>
       </c>
       <c r="C231">
         <v>13723.1</v>
@@ -5229,7 +5229,7 @@
         <v>43831</v>
       </c>
       <c r="B242">
-        <v>14171.31801566526</v>
+        <v>14171.31801566527</v>
       </c>
       <c r="C242">
         <v>14184.79999999999</v>
@@ -5262,7 +5262,7 @@
         <v>43922</v>
       </c>
       <c r="B245">
-        <v>11001.45006248666</v>
+        <v>11001.45006248667</v>
       </c>
       <c r="C245">
         <v>11783.29999999999</v>
@@ -5273,7 +5273,7 @@
         <v>43952</v>
       </c>
       <c r="B246">
-        <v>12777.42280684459</v>
+        <v>12777.4228068446</v>
       </c>
       <c r="C246">
         <v>12757.99999999999</v>
@@ -5295,7 +5295,7 @@
         <v>44013</v>
       </c>
       <c r="B248">
-        <v>13724.39811231239</v>
+        <v>13724.3981123124</v>
       </c>
       <c r="C248">
         <v>13667.29999999999</v>
@@ -5438,7 +5438,7 @@
         <v>44409</v>
       </c>
       <c r="B261">
-        <v>14808.32399129106</v>
+        <v>14808.32399129105</v>
       </c>
       <c r="C261">
         <v>14863</v>
@@ -5449,7 +5449,7 @@
         <v>44440</v>
       </c>
       <c r="B262">
-        <v>14865.31802882312</v>
+        <v>14865.31802882313</v>
       </c>
       <c r="C262">
         <v>14899.4</v>
@@ -5559,7 +5559,7 @@
         <v>44743</v>
       </c>
       <c r="B272">
-        <v>15044.236632833</v>
+        <v>15044.23663283299</v>
       </c>
       <c r="C272">
         <v>15069.1</v>
@@ -5581,7 +5581,7 @@
         <v>44805</v>
       </c>
       <c r="B274">
-        <v>15162.45117697048</v>
+        <v>15162.45117697047</v>
       </c>
       <c r="C274">
         <v>15176.7</v>
@@ -5592,7 +5592,7 @@
         <v>44835</v>
       </c>
       <c r="B275">
-        <v>15260.00479084224</v>
+        <v>15260.00479084225</v>
       </c>
       <c r="C275">
         <v>15202.7</v>
@@ -5636,7 +5636,7 @@
         <v>44958</v>
       </c>
       <c r="B279">
-        <v>15279.23738761561</v>
+        <v>15279.2373876156</v>
       </c>
       <c r="C279">
         <v>15325.5</v>
@@ -5691,7 +5691,7 @@
         <v>45108</v>
       </c>
       <c r="B284">
-        <v>15434.91718733836</v>
+        <v>15434.91718733837</v>
       </c>
       <c r="C284">
         <v>15448.3</v>
@@ -5735,7 +5735,7 @@
         <v>45231</v>
       </c>
       <c r="B288">
-        <v>15583.98581120782</v>
+        <v>15583.98581120781</v>
       </c>
       <c r="C288">
         <v>15584.29999999999</v>
@@ -5823,7 +5823,7 @@
         <v>45474</v>
       </c>
       <c r="B296">
-        <v>15872.88007831158</v>
+        <v>15872.88007831159</v>
       </c>
       <c r="C296">
         <v>15870.29999999999</v>
